--- a/data/misc_corrections.xlsx
+++ b/data/misc_corrections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/corra_joseph_epa_gov/Documents/Profile/Documents/Fossil Fuels/Fossil Fuels/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{B6056445-6866-4865-9923-2023EA13973D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8287650-D579-4C05-AC8F-D8C98B38AE1C}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{B6056445-6866-4865-9923-2023EA13973D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B44F6EF4-E3FF-44FE-B9B1-6728D77E8E84}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8421F8FA-45A9-4AAA-953B-13AF90DC74C2}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{8421F8FA-45A9-4AAA-953B-13AF90DC74C2}"/>
   </bookViews>
   <sheets>
     <sheet name="corrections" sheetId="1" r:id="rId1"/>
@@ -450,13 +450,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9DA5331-DFAB-4D03-8EE5-D0487E370D3B}">
-  <dimension ref="A1:AH21"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -559,85 +559,88 @@
       <c r="AH1">
         <v>2022</v>
       </c>
+      <c r="AI1">
+        <v>2023</v>
+      </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>59.292568208118979</v>
+        <v>59.292568144837638</v>
       </c>
       <c r="C2">
-        <v>68.103988777369921</v>
+        <v>68.103988777369949</v>
       </c>
       <c r="D2">
-        <v>78.591291501711424</v>
+        <v>78.591291501711396</v>
       </c>
       <c r="E2">
         <v>91.737080276773597</v>
       </c>
       <c r="F2">
-        <v>102.86819559326631</v>
+        <v>102.86819559326626</v>
       </c>
       <c r="G2">
-        <v>109.43931636217866</v>
+        <v>109.43931636217864</v>
       </c>
       <c r="H2">
         <v>78.803378262521903</v>
       </c>
       <c r="I2">
-        <v>99.915740825134094</v>
+        <v>99.915740825134066</v>
       </c>
       <c r="J2">
-        <v>110.45003235696942</v>
+        <v>110.45003235696939</v>
       </c>
       <c r="K2">
-        <v>116.27377463725651</v>
+        <v>116.27377128779456</v>
       </c>
       <c r="L2">
-        <v>132.00657596851812</v>
+        <v>132.00657147645796</v>
       </c>
       <c r="M2">
-        <v>138.12739529642127</v>
+        <v>138.12738981215131</v>
       </c>
       <c r="N2">
-        <v>163.74011497220897</v>
+        <v>163.74010799185194</v>
       </c>
       <c r="O2">
-        <v>222.88903423434519</v>
+        <v>222.88902838579065</v>
       </c>
       <c r="P2">
-        <v>278.83587961199629</v>
+        <v>278.83587849741861</v>
       </c>
       <c r="Q2">
-        <v>315.76705017769331</v>
+        <v>315.76704772748508</v>
       </c>
       <c r="R2">
-        <v>419.59886500495992</v>
+        <v>419.59886055730391</v>
       </c>
       <c r="S2">
-        <v>527.24813217258725</v>
+        <v>527.24812667899414</v>
       </c>
       <c r="T2">
-        <v>745.73380966143191</v>
+        <v>745.73380047948638</v>
       </c>
       <c r="U2">
-        <v>854.64492307927401</v>
+        <v>854.64491109260257</v>
       </c>
       <c r="V2">
-        <v>1003.5575337472352</v>
+        <v>1003.5575207636</v>
       </c>
       <c r="W2">
-        <v>1015.0464775511798</v>
+        <v>1015.0464664858799</v>
       </c>
       <c r="X2">
-        <v>1016.8477355386466</v>
+        <v>1016.8477198906728</v>
       </c>
       <c r="Y2">
-        <v>1030.163949979275</v>
+        <v>1030.1639348139765</v>
       </c>
       <c r="Z2">
-        <v>1081.0686275646119</v>
+        <v>1081.0686096970153</v>
       </c>
       <c r="AA2">
         <v>1083.7098559272808</v>
@@ -652,96 +655,99 @@
         <v>1148.2220033933766</v>
       </c>
       <c r="AE2">
-        <v>1150.2042903482761</v>
+        <v>1150.2042903482759</v>
       </c>
       <c r="AF2">
         <v>994.56499983933315</v>
       </c>
       <c r="AG2">
-        <v>1101.6685259577537</v>
+        <v>1101.6685259577534</v>
       </c>
       <c r="AH2">
-        <v>1094.9003699234224</v>
+        <v>1094.8994282194542</v>
+      </c>
+      <c r="AI2">
+        <v>1116.4335840509723</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1.5292960059058021</v>
+        <v>1.5292960454476157</v>
       </c>
       <c r="C3">
-        <v>2.3867553910896904</v>
+        <v>2.3867553910896775</v>
       </c>
       <c r="D3">
-        <v>1.9498259418735089</v>
+        <v>1.9498259418735233</v>
       </c>
       <c r="E3">
         <v>2.8405691869017047</v>
       </c>
       <c r="F3">
-        <v>3.1553012342937135</v>
+        <v>3.155301234293749</v>
       </c>
       <c r="G3">
-        <v>4.3388831492071445</v>
+        <v>4.3388831492071587</v>
       </c>
       <c r="H3">
-        <v>2.7266879564605668</v>
+        <v>2.7266879564605762</v>
       </c>
       <c r="I3">
-        <v>3.1457469547458574</v>
+        <v>3.1457469547458881</v>
       </c>
       <c r="J3">
-        <v>3.4574471716035142</v>
+        <v>3.4574471716035355</v>
       </c>
       <c r="K3">
-        <v>2.408077587374259</v>
+        <v>2.4080804083356089</v>
       </c>
       <c r="L3">
-        <v>3.4913844678314434</v>
+        <v>3.4913879327098809</v>
       </c>
       <c r="M3">
-        <v>4.9815113457806639</v>
+        <v>4.9815162125204324</v>
       </c>
       <c r="N3">
-        <v>6.5015829612620211</v>
+        <v>6.5015890522660076</v>
       </c>
       <c r="O3">
-        <v>8.8387947114935237</v>
+        <v>8.8387996474566606</v>
       </c>
       <c r="P3">
-        <v>12.938399106580322</v>
+        <v>12.938400101662541</v>
       </c>
       <c r="Q3">
-        <v>17.174540059612085</v>
+        <v>17.174542230878206</v>
       </c>
       <c r="R3">
-        <v>29.239615025568451</v>
+        <v>29.239618963767789</v>
       </c>
       <c r="S3">
-        <v>34.462531641674801</v>
+        <v>34.46253622035222</v>
       </c>
       <c r="T3">
-        <v>45.552594026063041</v>
+        <v>45.552601788148124</v>
       </c>
       <c r="U3">
-        <v>45.156970429709368</v>
+        <v>45.156980269751038</v>
       </c>
       <c r="V3">
-        <v>48.063352361195548</v>
+        <v>48.063363183810701</v>
       </c>
       <c r="W3">
-        <v>42.268289037155675</v>
+        <v>42.268298469001479</v>
       </c>
       <c r="X3">
-        <v>40.763336205509631</v>
+        <v>40.763349777288319</v>
       </c>
       <c r="Y3">
-        <v>53.531957941938757</v>
+        <v>53.531971107704621</v>
       </c>
       <c r="Z3">
-        <v>24.054336855936388</v>
+        <v>24.054351078375543</v>
       </c>
       <c r="AA3">
         <v>28.212102418291263</v>
@@ -756,96 +762,99 @@
         <v>20.51310741243449</v>
       </c>
       <c r="AE3">
-        <v>23.515154273488882</v>
+        <v>23.515154273488985</v>
       </c>
       <c r="AF3">
         <v>23.102871790312395</v>
       </c>
       <c r="AG3">
-        <v>22.041749991834653</v>
+        <v>22.041749991834703</v>
       </c>
       <c r="AH3">
-        <v>28.03787092256697</v>
+        <v>26.150161614080066</v>
+      </c>
+      <c r="AI3">
+        <v>24.125767610058457</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.91813578597521628</v>
+        <v>0.91813580971473696</v>
       </c>
       <c r="C4">
-        <v>1.05025583154038</v>
+        <v>1.0502558315403743</v>
       </c>
       <c r="D4">
-        <v>0.79888255641506034</v>
+        <v>0.79888255641506634</v>
       </c>
       <c r="E4">
         <v>0.4683505363246861</v>
       </c>
       <c r="F4">
-        <v>0.41350317243999257</v>
+        <v>0.41350317243999712</v>
       </c>
       <c r="G4">
-        <v>0.39280048861418587</v>
+        <v>0.39280048861418704</v>
       </c>
       <c r="H4">
-        <v>0.3619337810175296</v>
+        <v>0.36193378101753071</v>
       </c>
       <c r="I4">
-        <v>0.63451222012004449</v>
+        <v>0.6345122201200506</v>
       </c>
       <c r="J4">
-        <v>0.67552047142709204</v>
+        <v>0.67552047142709626</v>
       </c>
       <c r="K4">
-        <v>0.4511477753692269</v>
+        <v>0.4511483038698218</v>
       </c>
       <c r="L4">
-        <v>1.0350395636504546</v>
+        <v>1.0350405908321638</v>
       </c>
       <c r="M4">
-        <v>0.63209335779806408</v>
+        <v>0.63209397532830092</v>
       </c>
       <c r="N4">
-        <v>0.94930206652900317</v>
+        <v>0.9493029558820586</v>
       </c>
       <c r="O4">
-        <v>1.634171054161317</v>
+        <v>1.6341719667527219</v>
       </c>
       <c r="P4">
-        <v>1.5537212814234171</v>
+        <v>1.5537214009189133</v>
       </c>
       <c r="Q4">
-        <v>2.2064097626946273</v>
+        <v>2.2064100416367558</v>
       </c>
       <c r="R4">
-        <v>3.7825199694716138</v>
+        <v>3.7825204789283098</v>
       </c>
       <c r="S4">
-        <v>6.8863361857380614</v>
+        <v>6.8863371006537832</v>
       </c>
       <c r="T4">
-        <v>8.3325963125051032</v>
+        <v>8.332597732365441</v>
       </c>
       <c r="U4">
-        <v>9.8511064910166883</v>
+        <v>9.8511086376464885</v>
       </c>
       <c r="V4">
-        <v>9.5971138915692737</v>
+        <v>9.5971160525893655</v>
       </c>
       <c r="W4">
-        <v>7.320233411664411</v>
+        <v>7.3202350451185758</v>
       </c>
       <c r="X4">
-        <v>6.2359282558440654</v>
+        <v>6.2359303320391462</v>
       </c>
       <c r="Y4">
-        <v>8.1300920787863351</v>
+        <v>8.1300940783188196</v>
       </c>
       <c r="Z4">
-        <v>6.1650355794517333</v>
+        <v>6.1650392246091092</v>
       </c>
       <c r="AA4">
         <v>41.132041654427702</v>
@@ -860,19 +869,22 @@
         <v>27.895889194189088</v>
       </c>
       <c r="AE4">
-        <v>32.558555378235127</v>
+        <v>32.558555378235269</v>
       </c>
       <c r="AF4">
         <v>31.876128370354355</v>
       </c>
       <c r="AG4">
-        <v>31.242724050411745</v>
+        <v>31.242724050411816</v>
       </c>
       <c r="AH4">
-        <v>39.74175915401046</v>
+        <v>41.62941016646576</v>
+      </c>
+      <c r="AI4">
+        <v>38.406648338969362</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -907,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>17.747978702425556</v>
+        <v>17.747978702425552</v>
       </c>
       <c r="M5">
         <v>19.719976336028392</v>
@@ -922,10 +934,10 @@
         <v>19.719976336028392</v>
       </c>
       <c r="Q5">
-        <v>19.719976336028392</v>
+        <v>19.719976336028399</v>
       </c>
       <c r="R5">
-        <v>19.719976336028399</v>
+        <v>19.719976336028395</v>
       </c>
       <c r="S5">
         <v>19.719976336028395</v>
@@ -934,10 +946,10 @@
         <v>19.719976336028395</v>
       </c>
       <c r="U5">
+        <v>19.719976336028392</v>
+      </c>
+      <c r="V5">
         <v>19.719976336028395</v>
-      </c>
-      <c r="V5">
-        <v>19.719976336028392</v>
       </c>
       <c r="W5">
         <v>19.719976336028395</v>
@@ -949,34 +961,37 @@
         <v>19.719976336028395</v>
       </c>
       <c r="Z5">
-        <v>26.55327351607178</v>
+        <v>26.553273516071776</v>
       </c>
       <c r="AA5">
         <v>21.402553736935509</v>
       </c>
       <c r="AB5">
-        <v>15.929432064681521</v>
+        <v>15.929432064681524</v>
       </c>
       <c r="AC5">
         <v>17.112482745020706</v>
       </c>
       <c r="AD5">
-        <v>15.537684874778153</v>
+        <v>15.537684874778147</v>
       </c>
       <c r="AE5">
         <v>17.386107276671268</v>
       </c>
       <c r="AF5">
-        <v>15.711728002366396</v>
+        <v>15.711728002366394</v>
       </c>
       <c r="AG5">
         <v>16.420069019917172</v>
       </c>
       <c r="AH5">
-        <v>15.824896470124235</v>
+        <v>15.824896470124237</v>
+      </c>
+      <c r="AI5">
+        <v>10.521987773614674</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1079,8 +1094,11 @@
       <c r="AH6">
         <v>9.4640446919181898</v>
       </c>
+      <c r="AI6">
+        <v>9.4581343063049435</v>
+      </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1183,8 +1201,11 @@
       <c r="AH7">
         <v>0</v>
       </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1276,19 +1297,22 @@
         <v>364.83611784310114</v>
       </c>
       <c r="AE8">
-        <v>365.53435230295742</v>
+        <v>365.29231688418758</v>
       </c>
       <c r="AF8">
-        <v>378.72007701898383</v>
+        <v>378.51709100816026</v>
       </c>
       <c r="AG8">
-        <v>350.23363381117628</v>
+        <v>349.86425559872521</v>
       </c>
       <c r="AH8">
-        <v>373.20539516556141</v>
+        <v>372.96847780312459</v>
+      </c>
+      <c r="AI8">
+        <v>374.42777121358034</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1391,8 +1415,11 @@
       <c r="AH9">
         <v>0</v>
       </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1495,8 +1522,11 @@
       <c r="AH10">
         <v>0</v>
       </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1588,19 +1618,22 @@
         <v>399.89597594511588</v>
       </c>
       <c r="AE11">
-        <v>401.52702445369732</v>
+        <v>401.37115518304654</v>
       </c>
       <c r="AF11">
-        <v>334.03964633486987</v>
+        <v>334.50869148265144</v>
       </c>
       <c r="AG11">
-        <v>426.31606380854544</v>
+        <v>426.70624059715811</v>
       </c>
       <c r="AH11">
-        <v>412.29593580560106</v>
+        <v>412.6081099032146</v>
+      </c>
+      <c r="AI11">
+        <v>391.96540198075223</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1703,8 +1736,11 @@
       <c r="AH12">
         <v>12.589899570208365</v>
       </c>
+      <c r="AI12">
+        <v>10.766735215711874</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1802,13 +1838,16 @@
         <v>13.490252748026107</v>
       </c>
       <c r="AG13">
-        <v>15.358708807309499</v>
+        <v>13.979934937686567</v>
       </c>
       <c r="AH13">
         <v>13.004454172612423</v>
       </c>
+      <c r="AI13">
+        <v>12.201710087883262</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1906,13 +1945,16 @@
         <v>13.122245797290677</v>
       </c>
       <c r="AG14">
-        <v>14.434470377019746</v>
+        <v>15.090582666884281</v>
       </c>
       <c r="AH14">
-        <v>14.434470377019746</v>
+        <v>15.090582666884281</v>
+      </c>
+      <c r="AI14">
+        <v>12.072466133507422</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2015,8 +2057,11 @@
       <c r="AH15">
         <v>11.034701158805285</v>
       </c>
+      <c r="AI15">
+        <v>13.247614166802673</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2119,8 +2164,11 @@
       <c r="AH16">
         <v>1.0387726456667208</v>
       </c>
+      <c r="AI16">
+        <v>1.0387726456667208</v>
+      </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2128,7 +2176,7 @@
         <v>48.858205832242675</v>
       </c>
       <c r="C17">
-        <v>34.613650421211197</v>
+        <v>34.613650421211219</v>
       </c>
       <c r="D17">
         <v>98.177967493684832</v>
@@ -2223,8 +2271,11 @@
       <c r="AH17">
         <v>7.2213336304576501</v>
       </c>
+      <c r="AI17">
+        <v>7.2213336304576501</v>
+      </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2327,8 +2378,11 @@
       <c r="AH18">
         <v>44.009</v>
       </c>
+      <c r="AI18">
+        <v>44.009</v>
+      </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2429,10 +2483,13 @@
         <v>48.768848421495434</v>
       </c>
       <c r="AH19">
-        <v>45.847779855652632</v>
+        <v>49.25818194110397</v>
+      </c>
+      <c r="AI19">
+        <v>50.827906629809782</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2535,109 +2592,115 @@
       <c r="AH20">
         <v>0.28932098199494144</v>
       </c>
+      <c r="AI20">
+        <v>0.29854085716087991</v>
+      </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>35.508870113372502</v>
+        <v>35.488889284756993</v>
       </c>
       <c r="C21">
-        <v>30.654795613025964</v>
+        <v>30.637546170409742</v>
       </c>
       <c r="D21">
-        <v>33.739404531965391</v>
+        <v>33.720419381004795</v>
       </c>
       <c r="E21">
-        <v>32.495996285571202</v>
+        <v>32.477710799989737</v>
       </c>
       <c r="F21">
-        <v>24.150814016502515</v>
+        <v>24.137224362023275</v>
       </c>
       <c r="G21">
-        <v>36.082750842477516</v>
+        <v>36.062447091379326</v>
       </c>
       <c r="H21">
-        <v>89.955804287210356</v>
+        <v>89.905186188051047</v>
       </c>
       <c r="I21">
-        <v>62.385617593123825</v>
+        <v>62.350513228236359</v>
       </c>
       <c r="J21">
-        <v>53.131790836305527</v>
+        <v>53.101893596451205</v>
       </c>
       <c r="K21">
-        <v>44.953990446559132</v>
+        <v>44.928694852082927</v>
       </c>
       <c r="L21">
-        <v>72.022031502678786</v>
+        <v>71.981504731103072</v>
       </c>
       <c r="M21">
-        <v>62.313882501985688</v>
+        <v>62.278818502408569</v>
       </c>
       <c r="N21">
-        <v>69.320009736476038</v>
+        <v>69.281003391589579</v>
       </c>
       <c r="O21">
-        <v>70.180830830133544</v>
+        <v>70.141340101523085</v>
       </c>
       <c r="P21">
-        <v>81.204123168358947</v>
+        <v>81.158429637060436</v>
       </c>
       <c r="Q21">
-        <v>61.524796499466305</v>
+        <v>61.49017651830286</v>
       </c>
       <c r="R21">
-        <v>60.400946738302331</v>
+        <v>60.366959147000784</v>
       </c>
       <c r="S21">
-        <v>65.37457972387908</v>
+        <v>65.337793471061019</v>
       </c>
       <c r="T21">
-        <v>61.644354984696513</v>
+        <v>61.60966772801585</v>
       </c>
       <c r="U21">
-        <v>40.028180855074467</v>
+        <v>40.005657011907886</v>
       </c>
       <c r="V21">
-        <v>54.494757567929931</v>
+        <v>54.464093387179247</v>
       </c>
       <c r="W21">
-        <v>62.266059107893611</v>
+        <v>62.231022018523376</v>
       </c>
       <c r="X21">
-        <v>67.000575123009938</v>
+        <v>66.962873923157645</v>
       </c>
       <c r="Y21">
-        <v>63.963789598162599</v>
+        <v>63.927797196447784</v>
       </c>
       <c r="Z21">
-        <v>57.985865336652076</v>
+        <v>57.953236710798457</v>
       </c>
       <c r="AA21">
-        <v>54.399110779745762</v>
+        <v>54.368500419408868</v>
       </c>
       <c r="AB21">
-        <v>46.269133784091451</v>
+        <v>46.243098158925783</v>
       </c>
       <c r="AC21">
-        <v>50.812356222839448</v>
+        <v>50.783764128019264</v>
       </c>
       <c r="AD21">
-        <v>61.429149711282136</v>
+        <v>61.394583550532467</v>
       </c>
       <c r="AE21">
-        <v>58.942333218493758</v>
+        <v>58.909166388502349</v>
       </c>
       <c r="AF21">
-        <v>50.445094387926574</v>
+        <v>50.416708951210602</v>
       </c>
       <c r="AG21">
-        <v>56.297701451157046</v>
+        <v>56.266022754522901</v>
       </c>
       <c r="AH21">
-        <v>52.976769785822086</v>
+        <v>52.94695977625787</v>
+      </c>
+      <c r="AI21">
+        <v>54.634235811984873</v>
       </c>
     </row>
   </sheetData>
